--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
   <si>
     <t>Filename</t>
   </si>
@@ -808,667 +808,697 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9987,0.0001,0.0001,0.0000</t>
+    <t>0.9897,0.0008,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9922,0.0003,0.0000,0.0059</t>
+  </si>
+  <si>
+    <t>0.0010,0.0022,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9923,0.0004,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0340,0.0001,0.9902,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9907,0.0003,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.9962,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.2180,0.8017,0.0087,0.0008</t>
+  </si>
+  <si>
+    <t>0.0038,0.9962,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4861,0.0005,0.4446,0.0013</t>
+  </si>
+  <si>
+    <t>0.9034,0.0002,0.1034,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.0006,0.9921,0.0006</t>
+  </si>
+  <si>
+    <t>0.0169,0.0002,0.9887,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9984,0.0029</t>
+  </si>
+  <si>
+    <t>0.0230,0.9766,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.9947,0.0037,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.9889,0.0383,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9860,0.0157,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.9865,0.0603,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0112,0.9951,0.0002</t>
+  </si>
+  <si>
+    <t>0.1204,0.0004,0.8858,0.0007</t>
+  </si>
+  <si>
+    <t>0.0056,0.0057,0.9888,0.0002</t>
+  </si>
+  <si>
+    <t>0.5922,0.0001,0.6318,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.3342,0.9753,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.5407,0.0002,0.9914</t>
+  </si>
+  <si>
+    <t>0.0005,0.9978,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0133,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0188,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0028,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0031,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0029,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0041,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0038,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9387,0.9833,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0048,0.9914,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9903,0.0003,0.0054,0.0000</t>
+  </si>
+  <si>
+    <t>0.1303,0.0011,0.9113,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9977,0.0047</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9906,0.7446,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9936,0.2276,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.3916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.1235,0.9950</t>
+  </si>
+  <si>
+    <t>0.0000,0.0022,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0015,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.6713,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9758,0.5913,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.4362,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9580,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0068,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9843,0.0227,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9850,0.0188,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0057,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0001,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9977,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9969,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7193,0.3571,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.3578,0.0276,0.3060,0.0009</t>
+  </si>
+  <si>
+    <t>0.9881,0.0028,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0776,0.0637,0.2985,0.0272</t>
+  </si>
+  <si>
+    <t>0.0140,0.0099,0.9664,0.0021</t>
+  </si>
+  <si>
+    <t>0.0213,0.4391,0.0231,0.7154</t>
+  </si>
+  <si>
+    <t>0.0004,0.9987,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9893,0.9063,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9613,0.0423,0.0038,0.0016</t>
+  </si>
+  <si>
+    <t>0.8876,0.1256,0.0026,0.0014</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9946,0.0035,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.3310,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8424,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0322,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0119,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.5533,0.0002,0.4286,0.0012</t>
+  </si>
+  <si>
+    <t>0.0129,0.0000,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.7605,0.0004,0.3187,0.0003</t>
+  </si>
+  <si>
+    <t>0.0045,0.0001,0.0001,0.9982</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.3220,0.0006,0.0002,0.7865</t>
-  </si>
-  <si>
-    <t>0.1346,0.0004,0.0001,0.9416</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
+    <t>0.0000,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.7735,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.1666,0.8578,0.0007,0.0008</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9899,0.0002,0.0045,0.0000</t>
-  </si>
-  <si>
-    <t>0.0074,0.0033,0.9833,0.0007</t>
-  </si>
-  <si>
-    <t>0.0352,0.0002,0.9802,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.9486,0.0016,0.0253,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.9967,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.4487,0.6014,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.9985,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.4522,0.0010,0.5232,0.0026</t>
-  </si>
-  <si>
-    <t>0.6237,0.0003,0.4249,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0139,0.0001,0.9904,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0006</t>
-  </si>
-  <si>
-    <t>0.0255,0.9778,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0010,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0035</t>
-  </si>
-  <si>
-    <t>0.0015,0.9904,0.0154,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0000,0.0004</t>
+    <t>0.3020,0.7390,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1092,0.0001,0.0001,0.9629</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0060,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.9710,0.0000,0.0050,0.0021</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.8747,0.1076,0.0037,0.0015</t>
+  </si>
+  <si>
+    <t>0.9973,0.0017,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.1954,0.6405,0.0193,0.0018</t>
+  </si>
+  <si>
+    <t>0.9456,0.0098,0.0160,0.0012</t>
+  </si>
+  <si>
+    <t>0.9921,0.0057,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0025,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8388,0.1675,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.7436,0.3923,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9592,0.0317,0.0075,0.0070</t>
+  </si>
+  <si>
+    <t>0.9952,0.0066,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9723,0.0338,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0136,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9355,0.0289,0.0292,0.0110</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0064,0.9979,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0328,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0031,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0098,0.0010,0.9828,0.0013</t>
+  </si>
+  <si>
+    <t>0.1431,0.0007,0.9337,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.0093,0.9940,0.0005</t>
+  </si>
+  <si>
+    <t>0.0349,0.0050,0.9610,0.0005</t>
+  </si>
+  <si>
+    <t>0.0022,0.4331,0.7323,0.0005</t>
+  </si>
+  <si>
+    <t>0.4474,0.0014,0.4638,0.0002</t>
+  </si>
+  <si>
+    <t>0.9504,0.0148,0.0061,0.0014</t>
+  </si>
+  <si>
+    <t>0.0341,0.0031,0.9600,0.0025</t>
+  </si>
+  <si>
+    <t>0.0222,0.9826,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.9963,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7812,0.3707,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0087,0.9924,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.1617,0.8978,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9140,0.0035,0.0611,0.0003</t>
+  </si>
+  <si>
+    <t>0.9923,0.0008,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9806,0.0076,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.6757,0.0021,0.2974,0.0014</t>
+  </si>
+  <si>
+    <t>0.9290,0.0137,0.0206,0.0011</t>
+  </si>
+  <si>
+    <t>0.0038,0.0008,0.9916,0.0082</t>
+  </si>
+  <si>
+    <t>0.0039,0.0076,0.9878,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.0862,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.2210,0.9842,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0013,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0689,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0409,0.7608,0.1778,0.0007</t>
+  </si>
+  <si>
+    <t>0.7854,0.0009,0.1435,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0019,0.9961,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.0720,0.9920,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.9971,0.0006</t>
+  </si>
+  <si>
+    <t>0.8141,0.0002,0.1717,0.0006</t>
+  </si>
+  <si>
+    <t>0.8253,0.0001,0.2596,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0004,0.0003</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.6120,0.3763,0.0043,0.0017</t>
-  </si>
-  <si>
-    <t>0.0011,0.9953,0.0120,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.0112,0.9883,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.0007,0.9946,0.0018</t>
-  </si>
-  <si>
-    <t>0.0113,0.0311,0.9689,0.0003</t>
-  </si>
-  <si>
-    <t>0.0056,0.0014,0.9939,0.0005</t>
-  </si>
-  <si>
-    <t>0.0054,0.0408,0.9889,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9972,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9367,0.0006,0.9767</t>
-  </si>
-  <si>
-    <t>0.0023,0.9883,0.0026,0.0048</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0329,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0028,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9955,0.0032,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0045,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0010,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8749,0.9883,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0031,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9988,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0514,0.0048,0.9453,0.0014</t>
-  </si>
-  <si>
-    <t>0.0004,0.0448,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9859,0.6184,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.2724,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.4713,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.0144,0.9966</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0009,0.9996</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0062,0.9990</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0001,0.9988,0.0282,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9875,0.9836,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9846,0.9126,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.7179,0.9830,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9962,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0320,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9718,0.0483,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0074,0.0003,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0022,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0002,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0219,0.0002,0.9880,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0245,0.9805,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9980,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.2734,0.7716,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.9217,0.0202,0.0170,0.0014</t>
-  </si>
-  <si>
-    <t>0.6999,0.0166,0.1381,0.0002</t>
-  </si>
-  <si>
-    <t>0.0835,0.4083,0.0928,0.0069</t>
-  </si>
-  <si>
-    <t>0.0391,0.0069,0.9176,0.0051</t>
-  </si>
-  <si>
-    <t>0.0063,0.6500,0.0086,0.6593</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9841,0.9846,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6815,0.3440,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.6786,0.3307,0.0108,0.0027</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.1245,0.9781,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.6921,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0117,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0218,0.9948,0.0001</t>
-  </si>
-  <si>
-    <t>0.9934,0.0004,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9495,0.0008,0.0234,0.0013</t>
-  </si>
-  <si>
-    <t>0.0496,0.0000,0.9826,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0001,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0514,0.0006,0.0000,0.9874</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0264,0.9677,0.0027,0.0013</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.0089,0.9899,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0369,0.0000,0.0007,0.9847</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0016,0.9991,0.0012</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9982,0.0000,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.1875,0.2131,0.1305,0.0030</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.9938,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.8746,0.0085,0.0680,0.0018</t>
-  </si>
-  <si>
-    <t>0.9974,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9901,0.0140,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.4942,0.5997,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.6123,0.5265,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0962,0.0587,0.9215,0.0013</t>
-  </si>
-  <si>
-    <t>0.9981,0.0020,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0022,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9396,0.0689,0.0034,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0122,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9801,0.0104,0.0020,0.0048</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0038,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0017,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.0005,0.9931,0.0007</t>
-  </si>
-  <si>
-    <t>0.0187,0.0016,0.9884,0.0001</t>
-  </si>
-  <si>
-    <t>0.0111,0.0010,0.9835,0.0020</t>
-  </si>
-  <si>
-    <t>0.0162,0.0042,0.9735,0.0004</t>
-  </si>
-  <si>
-    <t>0.0186,0.4805,0.5745,0.0001</t>
-  </si>
-  <si>
-    <t>0.0309,0.0009,0.9598,0.0012</t>
-  </si>
-  <si>
-    <t>0.9881,0.0026,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.0445,0.0007,0.9499,0.0046</t>
-  </si>
-  <si>
-    <t>0.0068,0.9945,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0127,0.9908,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9857,0.0224,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9753,0.0380,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0044,0.9959,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.8533,0.0020,0.1264,0.0004</t>
-  </si>
-  <si>
-    <t>0.9919,0.0002,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0005,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9622,0.0022,0.0163,0.0005</t>
-  </si>
-  <si>
-    <t>0.5464,0.0004,0.3914,0.0027</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9957,0.0295</t>
-  </si>
-  <si>
-    <t>0.0007,0.0178,0.9971,0.0002</t>
-  </si>
-  <si>
-    <t>0.0048,0.0471,0.9843,0.0003</t>
-  </si>
-  <si>
-    <t>0.0098,0.0008,0.9854,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.8301,0.9598,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0029,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0033,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0572,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0099,0.0159,0.9618,0.0020</t>
-  </si>
-  <si>
-    <t>0.7706,0.0012,0.1328,0.0020</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0032,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0123,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9971,0.0006</t>
-  </si>
-  <si>
-    <t>0.6420,0.0004,0.3815,0.0003</t>
-  </si>
-  <si>
-    <t>0.0492,0.0001,0.9659,0.0005</t>
-  </si>
-  <si>
-    <t>0.9955,0.0003,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0009,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0193,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0072,0.9933,0.0013</t>
-  </si>
-  <si>
-    <t>0.0025,0.0010,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.0010,0.9570,0.0254</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9948,0.0007</t>
-  </si>
-  <si>
-    <t>0.6991,0.0001,0.0007,0.3362</t>
-  </si>
-  <si>
-    <t>0.0232,0.1466,0.0003,0.9606</t>
-  </si>
-  <si>
-    <t>0.0041,0.0001,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0001,0.0003</t>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0062,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0076,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0028,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0825,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1873,0.9947,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0091,0.0003,0.9892,0.0009</t>
+  </si>
+  <si>
+    <t>0.0374,0.0012,0.9623,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.0008,0.9941,0.0018</t>
+  </si>
+  <si>
+    <t>0.9496,0.0002,0.0011,0.0299</t>
+  </si>
+  <si>
+    <t>0.0296,0.0105,0.0000,0.9841</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0003</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1884,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1868,7 +1898,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1879,10 +1909,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1896,7 +1926,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1910,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1924,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1938,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1966,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1980,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1994,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2008,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2022,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2036,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2050,7 +2080,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2064,7 +2094,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2078,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2092,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2106,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2120,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2134,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2148,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2159,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,7 +2206,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2190,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2204,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2218,7 +2248,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2232,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2246,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2260,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2288,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2302,7 +2332,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2316,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2330,7 +2360,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2344,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2358,7 +2388,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2372,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2386,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2400,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2411,10 +2441,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2428,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2442,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2456,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2467,10 +2497,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2484,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2498,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2512,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2526,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2540,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2554,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2568,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2582,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2596,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2610,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2624,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2638,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2652,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2666,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2680,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2694,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2708,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2722,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2736,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2750,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2764,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2778,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2792,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2806,7 +2836,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2820,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2834,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2848,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2862,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2876,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2890,7 +2920,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2904,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2918,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2932,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2946,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2960,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2974,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2985,10 +3015,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3002,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3016,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3027,10 +3057,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3044,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,7 +3088,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3072,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3086,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3100,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3114,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3128,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3142,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3156,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3170,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3184,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3226,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3240,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3254,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3268,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3296,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3310,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3324,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3338,7 +3368,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3352,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3366,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3380,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3394,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3408,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3422,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3433,10 +3463,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3447,10 +3477,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3464,7 +3494,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3475,10 +3505,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3492,7 +3522,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3503,10 +3533,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3520,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3534,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>279</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3548,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3562,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3576,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,7 +3620,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3604,7 +3634,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3618,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>375</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3632,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3646,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3660,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>270</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3674,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3688,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3702,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3716,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3730,7 +3760,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3744,7 +3774,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3758,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3772,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3786,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3800,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3814,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3828,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3842,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3856,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3870,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>266</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3884,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,7 +3928,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3912,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>351</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3926,7 +3956,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3940,7 +3970,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3954,7 +3984,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3968,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3982,7 +4012,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3996,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4010,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4024,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4038,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4052,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4066,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4080,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,7 +4124,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4108,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4122,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4136,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4150,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>406</v>
+        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4164,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4178,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4192,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4206,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4220,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4234,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4248,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4259,10 +4289,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4273,10 +4303,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4287,10 +4317,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4304,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4318,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4332,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4346,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4360,7 +4390,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4374,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4388,7 +4418,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4402,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4416,7 +4446,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4430,7 +4460,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4444,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4458,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4472,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4486,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4500,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4514,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4542,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4553,10 +4583,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4570,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4584,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4598,7 +4628,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4612,7 +4642,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4626,7 +4656,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4637,10 +4667,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4654,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4668,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4682,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4696,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4710,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4724,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4738,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4752,7 +4782,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4766,7 +4796,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4780,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4791,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4808,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>271</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4822,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>273</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4836,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4850,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>453</v>
+        <v>355</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4864,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4878,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>273</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4892,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4906,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>456</v>
+        <v>273</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4920,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4931,10 +4961,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4948,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4962,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4976,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4990,7 +5020,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5004,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5018,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>313</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5032,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5046,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5060,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5074,7 +5104,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5085,10 +5115,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5102,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5116,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5130,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>407</v>
+        <v>479</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5144,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5158,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5186,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>471</v>
+        <v>273</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5200,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5214,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>378</v>
+        <v>482</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5228,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5242,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5256,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5270,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5284,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5298,7 +5328,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5312,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5326,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5340,7 +5370,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5354,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5368,7 +5398,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5382,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5396,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5410,7 +5440,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
